--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,11 +483,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="25" customWidth="1" min="32" max="32"/>
+    <col width="27" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="10" customWidth="1" min="35" max="35"/>
@@ -532,7 +532,7 @@
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -851,10 +851,8 @@
           <t>Sworaj Dangol</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9841710676</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9841710676</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -869,10 +867,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9841710676</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9841710676</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -889,10 +885,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.68979</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.68979</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -944,50 +938,245 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.31366</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.31366</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>2d 17h 2m</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr">
+        <is>
+          <t>2d 17h 2m</t>
+        </is>
+      </c>
+      <c r="AU2" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV2" s="3" t="inlineStr">
+        <is>
           <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS2" s="3" t="inlineStr">
-        <is>
-          <t>2d 17h 2m</t>
-        </is>
-      </c>
-      <c r="AT2" s="3" t="inlineStr">
-        <is>
-          <t>2d 17h 2m</t>
-        </is>
-      </c>
-      <c r="AU2" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV2" s="3" t="inlineStr">
-        <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 10:15 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357911</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Nilisha Acharya</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Nilisha Acharya</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9848938626</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 10:15:47 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9848938626</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 01:14:17 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 10:15:48 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Aarambha Family Fast Food Restaurant - Restaurant Mahantar Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>acharyanilisha@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Sameer Thapa</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>L43-4</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 1m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1228,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1125,7 +1314,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0</v>
@@ -1183,7 +1372,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1048,10 +1048,8 @@
           <t>Nilisha Acharya</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9848938626</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9848938626</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1066,10 +1064,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9848938626</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9848938626</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1137,10 +1133,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1151,7 +1145,7 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW3"/>
+  <dimension ref="A1:AW4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -520,7 +520,7 @@
     <col width="27" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="19" customWidth="1" min="38" max="38"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1171,6 +1171,213 @@
       <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 10:47 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wfi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>wfi 6</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360793</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Kamala Shrestha</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Kamala Shrestha</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9851069734</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 10:47:10 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9851069734</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 03:14:31 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 10:47:10 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.717448</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Maijubahal Bangalamukhi temple, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>05:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>L5-5</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.350308</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wfi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>19h 32m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wfi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1193,12 +1400,12 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
     <col width="35" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
   </cols>
@@ -1222,7 +1429,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1232,7 +1439,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1243,7 +1450,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1462,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0m</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1474,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>19h 32m</t>
         </is>
       </c>
     </row>
@@ -1308,14 +1515,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -1366,14 +1573,14 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -1449,6 +1656,73 @@
       <c r="M17" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360793</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Kamala Shrestha</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wfi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wfi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 10:47:10 AM</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 03:14:31 PM</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 10:47:10 AM</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>19h 32m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW4"/>
+  <dimension ref="A1:AW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1241,10 +1241,8 @@
           <t>Kamala Shrestha</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9851069734</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9851069734</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1259,10 +1257,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>9851069734</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v>9851069734</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1279,10 +1275,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.717448</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.717448</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1334,50 +1328,257 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>L5-5</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.350308</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.350308</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>19h 32m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
           <t>Case : wfi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>19h 32m</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:02 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357832</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Ram Bijay Yadav</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Ram Bijay Yadav</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9841821402</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:30:36 PM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9841821402</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:30:36 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:02:52 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.70173</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>putalisadak near raktakali driving centre, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>ramyadav2065@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>21:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>CDB282</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.323</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 32m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 32m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>Case : wfi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1429,7 +1630,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1439,7 +1640,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1450,7 +1651,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1663,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 11h 16m</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1675,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>19h 32m</t>
+          <t>1d 21h 2m</t>
         </is>
       </c>
     </row>
@@ -1515,14 +1716,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1573,14 +1774,14 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1692,14 +1893,14 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
           <t>Case : wfi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Case : wfi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
           <t>07 Oct 2026 10:47:10 AM</t>
@@ -1723,6 +1924,73 @@
       <c r="M18" s="3" t="inlineStr">
         <is>
           <t>19h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TKT1357832</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Ram Bijay Yadav</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:30:36 PM</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:30:36 PM</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:02:52 AM</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>2d 22h 32m</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>2d 22h 32m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1438,10 +1438,8 @@
           <t>Ram Bijay Yadav</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9841821402</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9841821402</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1456,10 +1454,8 @@
       </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>9841821402</t>
-        </is>
+      <c r="U5" s="3" t="n">
+        <v>9841821402</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1476,10 +1472,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.70173</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.70173</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1535,50 +1529,252 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>CDB282</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.323</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.32299999999999</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 32m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 32m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>2d 22h 32m</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>2d 22h 32m</t>
-        </is>
-      </c>
-      <c r="AU5" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV5" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:14 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr"/>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AC6" s="3" t="inlineStr"/>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 10:59 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AC7" s="3" t="inlineStr"/>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr"/>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr"/>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr"/>
+      <c r="AM7" s="3" t="inlineStr"/>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1602,7 +1798,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1630,7 +1826,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1651,7 +1847,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -1727,268 +1923,297 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C15" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>TKT1360793</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Kamala Shrestha</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Case : wfi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>07 Oct 2026 10:47:10 AM</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>06 Oct 2026 03:14:31 PM</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>07 Oct 2026 10:47:10 AM</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>19h 32m</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>TKT1357832</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Ram Bijay Yadav</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>04 Oct 2026 12:30:36 PM</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>04 Oct 2026 12:30:36 PM</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>07 Oct 2026 11:02:52 AM</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>2d 22h 32m</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>2d 22h 32m</t>
         </is>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,14 +494,14 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -511,14 +511,14 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="27" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1778,6 +1778,730 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:26 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr"/>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" s="3" t="inlineStr"/>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="AA8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AC8" s="3" t="inlineStr"/>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr"/>
+      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AG8" s="3" t="inlineStr"/>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr"/>
+      <c r="AM8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:22 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Adapter damage issue</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360721</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Sandip kumar Raut</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Sandip kumar Raut</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9823759370</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:20:12 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9817821214</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:28:58 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:22:27 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.704763</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Batishputali Dawrika hotel, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>06:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Ghimire</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L41-6</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.343163</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>2m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>20h 53m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:20 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Adapter damage issue</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360721</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Sandip kumar Raut</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Sandip kumar Raut</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9823759370</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:20:12 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9817821214</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:28:58 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:22:27 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.704763</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Batishputali Dawrika hotel, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>06:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Ghimire</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L41-6</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.343163</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>2m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>20h 53m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:19 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Adapter damage issue</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360721</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Sandip kumar Raut</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Sandip kumar Raut</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9823759370</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:20:12 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9817821214</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:28:58 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:22:27 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.704763</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Batishputali Dawrika hotel, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>06:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Ghimire</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L41-6</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.343163</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>2m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>20h 53m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1789,16 +2513,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1826,7 +2550,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -1836,7 +2560,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1847,7 +2571,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1859,7 +2583,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 11h 16m</t>
+          <t>14h 7m</t>
         </is>
       </c>
     </row>
@@ -1871,7 +2595,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 21h 2m</t>
+          <t>1d 6h 33m</t>
         </is>
       </c>
     </row>
@@ -1924,298 +2648,540 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
       <c r="B11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C16" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr"/>
-      <c r="B16" s="3" t="inlineStr"/>
-      <c r="C16" s="3" t="n">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>TKT1360793</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Kamala Shrestha</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Case : wfi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>07 Oct 2026 10:47:10 AM</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>06 Oct 2026 03:14:31 PM</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>07 Oct 2026 10:47:10 AM</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>19h 32m</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>TKT1357832</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Ram Bijay Yadav</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>04 Oct 2026 12:30:36 PM</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>04 Oct 2026 12:30:36 PM</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>07 Oct 2026 11:02:52 AM</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>2d 22h 32m</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>2d 22h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360721</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Sandip kumar Raut</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:20:12 AM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:28:58 PM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:22:27 AM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>2m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>20h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TKT1360721</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Sandip kumar Raut</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:20:12 AM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:28:58 PM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:22:27 AM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>2m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>20h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360721</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Sandip kumar Raut</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:20:12 AM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:28:58 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:22:27 AM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>2m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>20h 53m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1948,10 +1948,8 @@
           <t>Sandip kumar Raut</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9823759370</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9823759370</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -1966,10 +1964,8 @@
       </c>
       <c r="S9" s="3" t="inlineStr"/>
       <c r="T9" s="3" t="inlineStr"/>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>9817821214</t>
-        </is>
+      <c r="U9" s="3" t="n">
+        <v>9817821214</v>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
@@ -1986,10 +1982,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.704763</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.704763</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2041,25 +2035,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>L41-6</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.343163</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.343163</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2155,10 +2145,8 @@
           <t>Sandip kumar Raut</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9823759370</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9823759370</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2173,10 +2161,8 @@
       </c>
       <c r="S10" s="3" t="inlineStr"/>
       <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>9817821214</t>
-        </is>
+      <c r="U10" s="3" t="n">
+        <v>9817821214</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
@@ -2193,10 +2179,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.704763</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.704763</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2248,25 +2232,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>L41-6</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.343163</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.343163</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -2362,10 +2342,8 @@
           <t>Sandip kumar Raut</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9823759370</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9823759370</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2380,10 +2358,8 @@
       </c>
       <c r="S11" s="3" t="inlineStr"/>
       <c r="T11" s="3" t="inlineStr"/>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>9817821214</t>
-        </is>
+      <c r="U11" s="3" t="n">
+        <v>9817821214</v>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
@@ -2400,10 +2376,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.704763</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.704763</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -2455,25 +2429,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>L41-6</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.343163</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.343163</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -2522,7 +2492,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3017,7 +2987,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -3084,7 +3054,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -3151,7 +3121,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW11"/>
+  <dimension ref="A1:AW13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2472,6 +2472,312 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:50 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>one light blinking</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360410</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Sarswati chetri</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Sarswati chetri</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9767960591</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:50:46 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9767960591</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:13:00 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:50:46 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr"/>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Makalbari, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>10:37 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L30-3</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 37m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:55 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr"/>
+      <c r="V13" s="3" t="inlineStr"/>
+      <c r="W13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr"/>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr"/>
+      <c r="AA13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AC13" s="3" t="inlineStr"/>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr"/>
+      <c r="AN13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2483,7 +2789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2492,7 +2798,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2520,7 +2826,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2530,7 +2836,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2553,7 +2859,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>14h 7m</t>
+          <t>11h 46m</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2871,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 6h 33m</t>
+          <t>1d 5h 33m</t>
         </is>
       </c>
     </row>
@@ -2624,10 +2930,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -2731,171 +3037,127 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
-      <c r="B18" s="3" t="inlineStr"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
       <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1360793</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Kamala Shrestha</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : wfi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>07 Oct 2026 10:47:10 AM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>06 Oct 2026 03:14:31 PM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>07 Oct 2026 10:47:10 AM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>19h 32m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TKT1357832</t>
+          <t>TKT1360793</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Ram Bijay Yadav</t>
+          <t>Kamala Shrestha</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -2925,54 +3187,54 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wfi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:30:36 PM</t>
+          <t>07 Oct 2026 10:47:10 AM</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:30:36 PM</t>
+          <t>06 Oct 2026 03:14:31 PM</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:02:52 AM</t>
+          <t>07 Oct 2026 10:47:10 AM</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>2d 22h 32m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>2d 22h 32m</t>
+          <t>19h 32m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1360721</t>
+          <t>TKT1357832</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Sandip kumar Raut</t>
+          <t>Ram Bijay Yadav</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -2992,32 +3254,32 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:20:12 AM</t>
+          <t>04 Oct 2026 12:30:36 PM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 02:28:58 PM</t>
+          <t>04 Oct 2026 12:30:36 PM</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:22:27 AM</t>
+          <t>07 Oct 2026 11:02:52 AM</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>2d 22h 32m</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>20h 53m</t>
+          <t>2d 22h 32m</t>
         </is>
       </c>
     </row>
@@ -3152,6 +3414,140 @@
       <c r="M26" s="3" t="inlineStr">
         <is>
           <t>20h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1360721</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Sandip kumar Raut</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:20:12 AM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 02:28:58 PM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:22:27 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>2m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>20h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360410</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Sarswati chetri</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:50:46 AM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:13:00 AM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:50:46 AM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>1d 37m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2539,10 +2539,8 @@
           <t>Sarswati chetri</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9767960591</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9767960591</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2557,10 +2555,8 @@
       </c>
       <c r="S12" s="3" t="inlineStr"/>
       <c r="T12" s="3" t="inlineStr"/>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>9767960591</t>
-        </is>
+      <c r="U12" s="3" t="n">
+        <v>9767960591</v>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
@@ -2610,10 +2606,8 @@
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="AH12" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH12" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
@@ -2632,10 +2626,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
@@ -2646,7 +2638,7 @@
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : one light blinking   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -2798,7 +2790,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3517,7 +3509,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Case : one light blinking   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW13"/>
+  <dimension ref="A1:AW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2770,6 +2770,217 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 1:16 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358898</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Pankaj Karnami</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Pankaj Karnami</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9808363062</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:16:14 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9808363062</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:30:04 AM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:16:14 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.697944</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>M8X5+8QH, Sungabha Marg, Kathmandu 44600 Near by Bhotebahal Plaza, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>pkarnami123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>23:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>2,8</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.310046</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>2d 4h 46m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2781,7 +2992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2790,7 +3001,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2818,7 +3029,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -2828,7 +3039,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2839,7 +3050,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -2851,7 +3062,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>11h 46m</t>
+          <t>10h 5m</t>
         </is>
       </c>
     </row>
@@ -2863,7 +3074,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 5h 33m</t>
+          <t>1d 8h 52m</t>
         </is>
       </c>
     </row>
@@ -2904,14 +3115,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -2994,14 +3205,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -3543,6 +3754,73 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1358898</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Pankaj Karnami</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:16:14 PM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:30:04 AM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:16:14 PM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>2d 4h 46m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2837,10 +2837,8 @@
           <t>Pankaj Karnami</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9808363062</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9808363062</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -2855,10 +2853,8 @@
       </c>
       <c r="S14" s="3" t="inlineStr"/>
       <c r="T14" s="3" t="inlineStr"/>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t>9808363062</t>
-        </is>
+      <c r="U14" s="3" t="n">
+        <v>9808363062</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
@@ -2875,10 +2871,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.697944</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.697944</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -2934,25 +2928,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>2,8</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.310046</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.310046</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3001,7 +2991,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3787,7 +3777,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW14"/>
+  <dimension ref="A1:AW17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2971,6 +2971,623 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 1:49 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358277</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Sworaj Dangol</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Sworaj Dangol</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9841710676</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:49:36 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9841710676</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:16:34 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:49:36 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.68979</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Next to nightangel school,Kupandole,Lalitpur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>dongolsworaj@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>23:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Aayesha Maharjan</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.31366</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 33m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 1:53 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359556</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Puspa KC</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Puspa KC</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9849750351</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:34:34 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9849750351</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:34:34 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:53:35 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.67713</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Near by radhe radhe Vatbhatini, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>L64-1</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.395276</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 19m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 19m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 1:49 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359556</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Puspa KC</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Puspa KC</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9849750351</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:34:34 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9849750351</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:34:34 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:53:35 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.67713</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Near by radhe radhe Vatbhatini, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr"/>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>L64-1</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.395276</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 19m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 19m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2982,7 +3599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2991,7 +3608,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3019,7 +3636,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -3029,7 +3646,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -3040,7 +3657,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3669,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10h 5m</t>
+          <t>8h 49m</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3681,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 8h 52m</t>
+          <t>1d 13h 27m</t>
         </is>
       </c>
     </row>
@@ -3105,14 +3722,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3195,14 +3812,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3811,6 +4428,73 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358277</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Sworaj Dangol</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:49:36 PM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:16:34 PM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:49:36 PM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 33m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3038,10 +3038,8 @@
           <t>Sworaj Dangol</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9841710676</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9841710676</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3056,10 +3054,8 @@
       </c>
       <c r="S15" s="3" t="inlineStr"/>
       <c r="T15" s="3" t="inlineStr"/>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t>9841710676</t>
-        </is>
+      <c r="U15" s="3" t="n">
+        <v>9841710676</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
@@ -3076,10 +3072,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>27.68979</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>27.68979</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -3135,25 +3129,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.31366</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.31366</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -3239,20 +3229,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M16" s="3" t="inlineStr"/>
       <c r="N16" s="3" t="inlineStr">
         <is>
           <t>Puspa KC</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9849750351</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9849750351</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3267,10 +3251,8 @@
       </c>
       <c r="S16" s="3" t="inlineStr"/>
       <c r="T16" s="3" t="inlineStr"/>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t>9849750351</t>
-        </is>
+      <c r="U16" s="3" t="n">
+        <v>9849750351</v>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
@@ -3287,10 +3269,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.67713</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.67713</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -3338,25 +3318,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>L64-1</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.395276</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.395276</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -3442,20 +3418,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M17" s="3" t="inlineStr"/>
       <c r="N17" s="3" t="inlineStr">
         <is>
           <t>Puspa KC</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9849750351</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9849750351</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3470,10 +3440,8 @@
       </c>
       <c r="S17" s="3" t="inlineStr"/>
       <c r="T17" s="3" t="inlineStr"/>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t>9849750351</t>
-        </is>
+      <c r="U17" s="3" t="n">
+        <v>9849750351</v>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
@@ -3490,10 +3458,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.67713</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.67713</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -3541,25 +3507,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>L64-1</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.395276</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.395276</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -3608,7 +3570,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4461,7 +4423,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW17"/>
+  <dimension ref="A1:AW20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3550,6 +3550,627 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 2:14 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358369</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Tanushi Agrawal</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Tanushi Agrawal</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9813849811</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:14:46 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9813849811</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:04:41 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:14:46 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.68394</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Sanepa ( Inside Ring Road ) Near everest engineering college, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>tanushi245@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>00:14 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Aayesha Maharjan</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.30652</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 10m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 2:02 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359809</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Ashutosh Regmi</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Ashutosh Regmi</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9867171444</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:13:09 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9867171444</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 06:58:32 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:13:09 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.70175</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>Tika Kathayat</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>27.655793801439316, 85.34194749764016, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>regmiashutosh3@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Rabindra Bohora</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>CDB091A</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.3341</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 14m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 2:00 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358082</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Sarita Kathet</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Sarita Kathet</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9861963449</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:31:51 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>CHB9861963449</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:31:51 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:00:30 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Bazar Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>9861963449@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>CDB187</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 28m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 28m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3561,7 +4182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3570,7 +4191,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3598,7 +4219,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -3608,7 +4229,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -3619,7 +4240,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -3631,7 +4252,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8h 49m</t>
+          <t>14h 12m</t>
         </is>
       </c>
     </row>
@@ -3643,7 +4264,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 13h 27m</t>
+          <t>1d 20h 2m</t>
         </is>
       </c>
     </row>
@@ -3684,14 +4305,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -3774,14 +4395,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -4457,6 +5078,140 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1358369</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Tanushi Agrawal</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:14:46 PM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:04:41 PM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:14:46 PM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>2d 21h 10m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358082</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Sarita Kathet</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:31:51 PM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:31:51 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:00:30 PM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 28m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 28m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW20"/>
+  <dimension ref="A1:AW22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -523,7 +523,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -3617,10 +3617,8 @@
           <t>Tanushi Agrawal</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9813849811</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9813849811</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -3655,10 +3653,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.68394</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.68394</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -3714,25 +3710,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>3,4</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.30652</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.30652000000001</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -3828,10 +3820,8 @@
           <t>Ashutosh Regmi</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9867171444</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9867171444</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -3866,10 +3856,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>27.70175</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>27.70175</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -3921,25 +3909,21 @@
           <t>Rabindra Bohora</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>CDB091A</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.3341</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.33410000000001</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -4035,10 +4019,8 @@
           <t>Sarita Kathet</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9861963449</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9861963449</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4128,10 +4110,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
@@ -4142,30 +4122,432 @@
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 28m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 28m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS20" s="3" t="inlineStr">
-        <is>
-          <t>2d 23h 28m</t>
-        </is>
-      </c>
-      <c r="AT20" s="3" t="inlineStr">
-        <is>
-          <t>2d 23h 28m</t>
-        </is>
-      </c>
-      <c r="AU20" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV20" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 2:24 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357434</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Santa Laxmi Dangol</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Santa Laxmi Dangol</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9814826224</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 09:43:25 AM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>LTP9869647958</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 09:29:52 AM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:24:50 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Sanepa Near Nabil Bank, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>9869647958@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr"/>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>3d 4h 41m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>3d 4h 54m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 2:28 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361680</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Pranish Shrestha</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Pranish Shrestha</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9818730623</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:28:56 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>BKT9818730623</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:12:30 AM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:28:56 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Supreme M9JR+PVM, Bhaktapur Road, Madhyapur Thimi 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>pranishstha45@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>03:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>4,1</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -4182,7 +4564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4219,7 +4601,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -4229,7 +4611,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -4240,7 +4622,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4634,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>14h 12m</t>
+          <t>12h 55m</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4646,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 20h 2m</t>
+          <t>1d 16h 19m</t>
         </is>
       </c>
     </row>
@@ -4305,14 +4687,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -4335,97 +4717,92 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>54.5%</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -4437,14 +4814,14 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -4453,248 +4830,160 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
       <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1360793</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Kamala Shrestha</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : wfi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>07 Oct 2026 10:47:10 AM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>06 Oct 2026 03:14:31 PM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>07 Oct 2026 10:47:10 AM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>19h 32m</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1357832</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Ram Bijay Yadav</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 12:30:36 PM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 12:30:36 PM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>07 Oct 2026 11:02:52 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>2d 22h 32m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>2d 22h 32m</t>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1360721</t>
+          <t>TKT1360793</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Sandip kumar Raut</t>
+          <t>Kamala Shrestha</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -4714,54 +5003,54 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+          <t>Case : wfi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:20:12 AM</t>
+          <t>07 Oct 2026 10:47:10 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 02:28:58 PM</t>
+          <t>06 Oct 2026 03:14:31 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:22:27 AM</t>
+          <t>07 Oct 2026 10:47:10 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>20h 53m</t>
+          <t>19h 32m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1360721</t>
+          <t>TKT1357832</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Sandip kumar Raut</t>
+          <t>Ram Bijay Yadav</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -4781,32 +5070,32 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:20:12 AM</t>
+          <t>04 Oct 2026 12:30:36 PM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 02:28:58 PM</t>
+          <t>04 Oct 2026 12:30:36 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:22:27 AM</t>
+          <t>07 Oct 2026 11:02:52 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>2d 22h 32m</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>20h 53m</t>
+          <t>2d 22h 32m</t>
         </is>
       </c>
     </row>
@@ -4880,12 +5169,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1360410</t>
+          <t>TKT1360721</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Sarswati chetri</t>
+          <t>Sandip kumar Raut</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -4895,7 +5184,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -4915,54 +5204,54 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : one light blinking   has been updated by Sabin Giri</t>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:50:46 AM</t>
+          <t>07 Oct 2026 11:20:12 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 11:13:00 AM</t>
+          <t>06 Oct 2026 02:28:58 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:50:46 AM</t>
+          <t>07 Oct 2026 11:22:27 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1d 37m</t>
+          <t>20h 53m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1358898</t>
+          <t>TKT1360721</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Pankaj Karnami</t>
+          <t>Sandip kumar Raut</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -4982,54 +5271,54 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 01:16:14 PM</t>
+          <t>07 Oct 2026 11:20:12 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 08:30:04 AM</t>
+          <t>06 Oct 2026 02:28:58 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 01:16:14 PM</t>
+          <t>07 Oct 2026 11:22:27 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2m</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>2d 4h 46m</t>
+          <t>20h 53m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1358277</t>
+          <t>TKT1360410</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Sworaj Dangol</t>
+          <t>Sarswati chetri</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -5049,22 +5338,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : one light blinking   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 01:49:36 PM</t>
+          <t>07 Oct 2026 11:50:46 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 04:16:34 PM</t>
+          <t>06 Oct 2026 11:13:00 AM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 01:49:36 PM</t>
+          <t>07 Oct 2026 11:50:46 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -5074,19 +5363,19 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>2d 21h 33m</t>
+          <t>1d 37m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1358369</t>
+          <t>TKT1358898</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Tanushi Agrawal</t>
+          <t>Pankaj Karnami</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -5111,27 +5400,27 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:14:46 PM</t>
+          <t>07 Oct 2026 01:16:14 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 05:04:41 PM</t>
+          <t>05 Oct 2026 08:30:04 AM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:14:46 PM</t>
+          <t>07 Oct 2026 01:16:14 PM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -5141,74 +5430,275 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>2d 21h 10m</t>
+          <t>2d 4h 46m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
+          <t>TKT1358277</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Sworaj Dangol</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:49:36 PM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:16:34 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:49:36 PM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1358369</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Tanushi Agrawal</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:14:46 PM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:04:41 PM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:14:46 PM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>2d 21h 10m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
           <t>TKT1358082</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Sarita Kathet</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>04 Oct 2026 02:31:51 PM</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>04 Oct 2026 02:31:51 PM</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>07 Oct 2026 02:00:30 PM</t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t>2d 23h 28m</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t>2d 23h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1361680</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Pranish Shrestha</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:28:56 PM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:12:30 AM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:28:56 PM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW22"/>
+  <dimension ref="A1:AW23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4218,10 +4218,8 @@
           <t>Santa Laxmi Dangol</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9814826224</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9814826224</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4307,10 +4305,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
@@ -4321,7 +4317,7 @@
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -4417,10 +4413,8 @@
           <t>Pranish Shrestha</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9818730623</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9818730623</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4510,10 +4504,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
@@ -4524,30 +4516,241 @@
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS22" s="3" t="inlineStr">
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 2:47 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359441</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Shivam Rajbanshi</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Shivam Rajbanshi</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9841080394</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:47:08 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9843730947</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 02:08:34 PM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:47:08 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.68844</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Hanumanthan,Kupondole Rd, Lalitpur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>shivamvip984@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>20:39 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>CDB592</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.31594</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT22" s="3" t="inlineStr">
-        <is>
-          <t>3h 16m</t>
-        </is>
-      </c>
-      <c r="AU22" s="3" t="inlineStr">
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>2d 38m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV22" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW22" s="3" t="inlineStr">
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -4564,7 +4767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4601,7 +4804,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -4611,7 +4814,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -4622,7 +4825,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4837,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>12h 55m</t>
+          <t>11h 50m</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4849,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 16h 19m</t>
+          <t>1d 17h 1m</t>
         </is>
       </c>
     </row>
@@ -4687,14 +4890,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -4795,14 +4998,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -5668,14 +5871,14 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
           <t>07 Oct 2026 02:28:56 PM</t>
@@ -5699,6 +5902,73 @@
       <c r="M35" s="5" t="inlineStr">
         <is>
           <t>3h 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359441</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Shivam Rajbanshi</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:47:08 PM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 02:08:34 PM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:47:08 PM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>2d 38m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4612,10 +4612,8 @@
           <t>Shivam Rajbanshi</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9841080394</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9841080394</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -4650,10 +4648,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.68844</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.68844</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -4709,25 +4705,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>CDB592</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.31594</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.31594</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -4776,7 +4768,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5938,7 +5930,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW23"/>
+  <dimension ref="A1:AW30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -527,9 +527,9 @@
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4748,6 +4748,1211 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 3:04 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr"/>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr"/>
+      <c r="V24" s="3" t="inlineStr"/>
+      <c r="W24" s="3" t="inlineStr"/>
+      <c r="X24" s="3" t="inlineStr"/>
+      <c r="Y24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="inlineStr"/>
+      <c r="AA24" s="3" t="inlineStr"/>
+      <c r="AB24" s="3" t="inlineStr"/>
+      <c r="AC24" s="3" t="inlineStr"/>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr"/>
+      <c r="AF24" s="3" t="inlineStr"/>
+      <c r="AG24" s="3" t="inlineStr"/>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr"/>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr"/>
+      <c r="AM24" s="3" t="inlineStr"/>
+      <c r="AN24" s="3" t="inlineStr"/>
+      <c r="AO24" s="3" t="inlineStr"/>
+      <c r="AP24" s="3" t="inlineStr"/>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 3:02 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr"/>
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr"/>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr"/>
+      <c r="V25" s="3" t="inlineStr"/>
+      <c r="W25" s="3" t="inlineStr"/>
+      <c r="X25" s="3" t="inlineStr"/>
+      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Z25" s="3" t="inlineStr"/>
+      <c r="AA25" s="3" t="inlineStr"/>
+      <c r="AB25" s="3" t="inlineStr"/>
+      <c r="AC25" s="3" t="inlineStr"/>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr"/>
+      <c r="AF25" s="3" t="inlineStr"/>
+      <c r="AG25" s="3" t="inlineStr"/>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr"/>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr"/>
+      <c r="AM25" s="3" t="inlineStr"/>
+      <c r="AN25" s="3" t="inlineStr"/>
+      <c r="AO25" s="3" t="inlineStr"/>
+      <c r="AP25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 3:07 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>router change</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358408</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh maharhatn</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9851234730</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:52:04 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>LTP9851234730</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:30:07 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:07:24 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.678663629123296</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>lalitpur balkumari , , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr">
+        <is>
+          <t>raje6@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr"/>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>CDB624</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.31776428222658</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 15m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 37m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 3:04 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>router change</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358408</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh maharhatn</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9851234730</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:52:04 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>LTP9851234730</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:30:07 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:07:24 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.678663629123296</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>lalitpur balkumari , , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>raje6@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr"/>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>CDB624</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.31776428222658</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 15m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 37m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 3:09 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357376</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Goma Adhikari</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Goma Adhikari</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9813097646</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:09:55 PM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>9813097646</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 08:51:00 AM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:09:55 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>Near lkapuri Colony - Housing society P8Q9+WVH Prayas marg Tokha 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr"/>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>L27-7</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>3d 6h 18m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 3:01 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357376</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Goma Adhikari</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Goma Adhikari</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9813097646</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:09:55 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9813097646</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 08:51:00 AM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:09:55 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Near lkapuri Colony - Housing society P8Q9+WVH Prayas marg Tokha 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr"/>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr"/>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>L27-7</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>3d 6h 18m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 3:00 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357376</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Goma Adhikari</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Goma Adhikari</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9813097646</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:09:55 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9813097646</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 08:51:00 AM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:09:55 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>Near lkapuri Colony - Housing society P8Q9+WVH Prayas marg Tokha 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr"/>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>L27-7</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>3d 6h 18m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4796,7 +6001,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -4817,7 +6022,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>41.4%</t>
         </is>
       </c>
     </row>
@@ -4882,14 +6087,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -4990,14 +6195,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>8</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW30"/>
+  <dimension ref="A1:AW33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="21" customWidth="1" min="25" max="25"/>
+    <col width="19" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -5021,10 +5021,8 @@
           <t>Rajesh maharhatn</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9851234730</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9851234730</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5059,10 +5057,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>27.678663629123296</t>
-        </is>
+      <c r="Y26" s="3" t="n">
+        <v>27.6786636291233</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -5114,25 +5110,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>CDB624</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.31776428222658</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.31776428222658</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -5228,10 +5220,8 @@
           <t>Rajesh maharhatn</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9851234730</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9851234730</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -5266,10 +5256,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>27.678663629123296</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>27.6786636291233</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -5321,25 +5309,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>CDB624</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.31776428222658</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.31776428222658</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -5435,10 +5419,8 @@
           <t>Goma Adhikari</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9813097646</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9813097646</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -5520,10 +5502,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
@@ -5534,7 +5514,7 @@
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
@@ -5630,10 +5610,8 @@
           <t>Goma Adhikari</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9813097646</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9813097646</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -5715,10 +5693,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
@@ -5729,7 +5705,7 @@
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -5825,10 +5801,8 @@
           <t>Goma Adhikari</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9813097646</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9813097646</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -5910,10 +5884,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -5924,30 +5896,339 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>3d 6h 18m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS30" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT30" s="3" t="inlineStr">
-        <is>
-          <t>3d 6h 18m</t>
-        </is>
-      </c>
-      <c r="AU30" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV30" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 3:29 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr"/>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr"/>
+      <c r="V31" s="3" t="inlineStr"/>
+      <c r="W31" s="3" t="inlineStr"/>
+      <c r="X31" s="3" t="inlineStr"/>
+      <c r="Y31" s="3" t="inlineStr"/>
+      <c r="Z31" s="3" t="inlineStr"/>
+      <c r="AA31" s="3" t="inlineStr"/>
+      <c r="AB31" s="3" t="inlineStr"/>
+      <c r="AC31" s="3" t="inlineStr"/>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr"/>
+      <c r="AF31" s="3" t="inlineStr"/>
+      <c r="AG31" s="3" t="inlineStr"/>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr"/>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr"/>
+      <c r="AM31" s="3" t="inlineStr"/>
+      <c r="AN31" s="3" t="inlineStr"/>
+      <c r="AO31" s="3" t="inlineStr"/>
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 3:26 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="inlineStr"/>
+      <c r="L32" s="3" t="inlineStr"/>
+      <c r="M32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="inlineStr"/>
+      <c r="P32" s="3" t="inlineStr"/>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr"/>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="3" t="inlineStr"/>
+      <c r="W32" s="3" t="inlineStr"/>
+      <c r="X32" s="3" t="inlineStr"/>
+      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Z32" s="3" t="inlineStr"/>
+      <c r="AA32" s="3" t="inlineStr"/>
+      <c r="AB32" s="3" t="inlineStr"/>
+      <c r="AC32" s="3" t="inlineStr"/>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr"/>
+      <c r="AF32" s="3" t="inlineStr"/>
+      <c r="AG32" s="3" t="inlineStr"/>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr"/>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr"/>
+      <c r="AM32" s="3" t="inlineStr"/>
+      <c r="AN32" s="3" t="inlineStr"/>
+      <c r="AO32" s="3" t="inlineStr"/>
+      <c r="AP32" s="3" t="inlineStr"/>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 3:29 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="inlineStr"/>
+      <c r="L33" s="3" t="inlineStr"/>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr"/>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr"/>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr"/>
+      <c r="V33" s="3" t="inlineStr"/>
+      <c r="W33" s="3" t="inlineStr"/>
+      <c r="X33" s="3" t="inlineStr"/>
+      <c r="Y33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="inlineStr"/>
+      <c r="AA33" s="3" t="inlineStr"/>
+      <c r="AB33" s="3" t="inlineStr"/>
+      <c r="AC33" s="3" t="inlineStr"/>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr"/>
+      <c r="AF33" s="3" t="inlineStr"/>
+      <c r="AG33" s="3" t="inlineStr"/>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr"/>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr"/>
+      <c r="AM33" s="3" t="inlineStr"/>
+      <c r="AN33" s="3" t="inlineStr"/>
+      <c r="AO33" s="3" t="inlineStr"/>
+      <c r="AP33" s="3" t="inlineStr"/>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -6001,7 +6282,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -6022,7 +6303,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW33"/>
+  <dimension ref="A1:AW34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -512,10 +512,10 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="19" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="27" customWidth="1" min="32" max="32"/>
     <col width="30" customWidth="1" min="33" max="33"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -6234,6 +6234,209 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 3:41 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router setup  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Router setup</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359387</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Maharjan</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Maharjan</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9803161521</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:41:20 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9803161521</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:36:59 PM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:41:20 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr"/>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-customer care</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Near Patan Music Center, Patan Sundhara, Lalitpur 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>sunealcha@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>22:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr"/>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>4,9</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr"/>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router setup  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 4m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router setup  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6245,7 +6448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6254,7 +6457,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6282,7 +6485,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -6292,7 +6495,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -6303,7 +6506,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>39.4%</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6518,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>11h 50m</t>
+          <t>10h 55m</t>
         </is>
       </c>
     </row>
@@ -6327,7 +6530,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 17h 1m</t>
+          <t>1d 17h 43m</t>
         </is>
       </c>
     </row>
@@ -6368,14 +6571,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.4%</t>
         </is>
       </c>
     </row>
@@ -6476,14 +6679,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.4%</t>
         </is>
       </c>
     </row>
@@ -7450,6 +7653,73 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1359387</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Sunil Maharjan</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router setup  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router setup  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:41:20 PM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:36:59 PM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:41:20 PM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>2d 2h 4m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW34"/>
+  <dimension ref="A1:AW37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -517,8 +517,8 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="11" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="27" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -6301,10 +6301,8 @@
           <t>Sunil Maharjan</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9803161521</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9803161521</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -6394,10 +6392,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
@@ -6408,30 +6404,659 @@
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 4m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
           <t>Case : Router setup  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS34" s="3" t="inlineStr">
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 3:53 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359234</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Ram Sharan Khatri</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Ram Sharan Khatri</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9841367090</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:52:19 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9841367090</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:58:54 AM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:53:15 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>27.6851</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Near to Guna Airlines Pvt. Ltd. , Aaloknagar , Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>ramthuldai@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr"/>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>2,6</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>85.33957</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 54m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 3:47 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : lan port not working  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>lan port not working</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360830</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Chandan shrestha</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Chandan shrestha</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9849210578</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 06:25:23 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9818108774</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 03:37:04 PM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:47:51 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.73385</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Banasthali Kharibot opposite of Ballchi Dhurbe Futsal Ground, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>shresthachandan99@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>General Query &amp; Feedback</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>10:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Ghimire</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>CDB436</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.29008</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : lan port not working  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>21h 22m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>1d 10m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : lan port not working  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 3:47 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : nettv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>nettv issue</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360404</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Manju Ghising</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Manju Ghising</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9819354646</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:47:23 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9819354646</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:08:05 AM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:47:23 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.67617</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Near Glowing kids montessori, M9GG+MP6, Madhyapur Thimi 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr"/>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>14:39 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Shakul Dahal</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>L28-2</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.37756</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : nettv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>2d 2h 4m</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 39m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV34" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router setup  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW34" s="3" t="inlineStr">
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : nettv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -6448,13 +7073,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -6485,7 +7110,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -6495,7 +7120,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -6506,7 +7131,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -6518,7 +7143,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10h 55m</t>
+          <t>10h 54m</t>
         </is>
       </c>
     </row>
@@ -6530,7 +7155,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 17h 43m</t>
+          <t>1d 15h 40m</t>
         </is>
       </c>
     </row>
@@ -6571,14 +7196,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6589,10 +7214,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -6607,7 +7232,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -6675,41 +7300,41 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>General Query &amp; Feedback</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>47.4%</t>
         </is>
       </c>
     </row>
@@ -6721,7 +7346,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -6739,336 +7364,204 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="5" t="inlineStr"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
       <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>nan%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Detailed Solved / Handled Tickets List</t>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
+      <c r="A24" s="3" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1360793</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Kamala Shrestha</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : wfi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>07 Oct 2026 10:47:10 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>06 Oct 2026 03:14:31 PM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>07 Oct 2026 10:47:10 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>19h 32m</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1357832</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Ram Bijay Yadav</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 12:30:36 PM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 12:30:36 PM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>07 Oct 2026 11:02:52 AM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>2d 22h 32m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>2d 22h 32m</t>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TKT1360721</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Sandip kumar Raut</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Router Adaptor damage Issue</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>07 Oct 2026 11:20:12 AM</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>06 Oct 2026 02:28:58 PM</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>07 Oct 2026 11:22:27 AM</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>2m</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>20h 53m</t>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1360721</t>
+          <t>TKT1360793</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Sandip kumar Raut</t>
+          <t>Kamala Shrestha</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -7088,54 +7581,54 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+          <t>Case : wfi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:20:12 AM</t>
+          <t>07 Oct 2026 10:47:10 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 02:28:58 PM</t>
+          <t>06 Oct 2026 03:14:31 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:22:27 AM</t>
+          <t>07 Oct 2026 10:47:10 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>20h 53m</t>
+          <t>19h 32m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1360721</t>
+          <t>TKT1357832</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Sandip kumar Raut</t>
+          <t>Ram Bijay Yadav</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -7155,44 +7648,44 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:20:12 AM</t>
+          <t>04 Oct 2026 12:30:36 PM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 02:28:58 PM</t>
+          <t>04 Oct 2026 12:30:36 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:22:27 AM</t>
+          <t>07 Oct 2026 11:02:52 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>2d 22h 32m</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>20h 53m</t>
+          <t>2d 22h 32m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1360410</t>
+          <t>TKT1360721</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Sarswati chetri</t>
+          <t>Sandip kumar Raut</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -7202,7 +7695,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -7222,54 +7715,54 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : one light blinking   has been updated by Sabin Giri</t>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:50:46 AM</t>
+          <t>07 Oct 2026 11:20:12 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 11:13:00 AM</t>
+          <t>06 Oct 2026 02:28:58 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:50:46 AM</t>
+          <t>07 Oct 2026 11:22:27 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1d 37m</t>
+          <t>20h 53m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1358898</t>
+          <t>TKT1360721</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Pankaj Karnami</t>
+          <t>Sandip kumar Raut</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -7289,54 +7782,54 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 01:16:14 PM</t>
+          <t>07 Oct 2026 11:20:12 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 08:30:04 AM</t>
+          <t>06 Oct 2026 02:28:58 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 01:16:14 PM</t>
+          <t>07 Oct 2026 11:22:27 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>2d 4h 46m</t>
+          <t>20h 53m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1358277</t>
+          <t>TKT1360721</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Sworaj Dangol</t>
+          <t>Sandip kumar Raut</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -7356,54 +7849,54 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Adapter damage issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 01:49:36 PM</t>
+          <t>07 Oct 2026 11:20:12 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 04:16:34 PM</t>
+          <t>06 Oct 2026 02:28:58 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 01:49:36 PM</t>
+          <t>07 Oct 2026 11:22:27 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2d 21h 33m</t>
+          <t>20h 53m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1358369</t>
+          <t>TKT1360410</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Tanushi Agrawal</t>
+          <t>Sarswati chetri</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -7423,22 +7916,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : one light blinking   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:14:46 PM</t>
+          <t>07 Oct 2026 11:50:46 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 05:04:41 PM</t>
+          <t>06 Oct 2026 11:13:00 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:14:46 PM</t>
+          <t>07 Oct 2026 11:50:46 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -7448,19 +7941,19 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>2d 21h 10m</t>
+          <t>1d 37m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1358082</t>
+          <t>TKT1358898</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Sarita Kathet</t>
+          <t>Pankaj Karnami</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -7475,12 +7968,12 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -7490,44 +7983,44 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:31:51 PM</t>
+          <t>07 Oct 2026 01:16:14 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:31:51 PM</t>
+          <t>05 Oct 2026 08:30:04 AM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:00:30 PM</t>
+          <t>07 Oct 2026 01:16:14 PM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2d 23h 28m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2d 23h 28m</t>
+          <t>2d 4h 46m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1361680</t>
+          <t>TKT1358277</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Pranish Shrestha</t>
+          <t>Sworaj Dangol</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -7557,22 +8050,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:28:56 PM</t>
+          <t>07 Oct 2026 01:49:36 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:12:30 AM</t>
+          <t>04 Oct 2026 04:16:34 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:28:56 PM</t>
+          <t>07 Oct 2026 01:49:36 PM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -7582,19 +8075,19 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>3h 16m</t>
+          <t>2d 21h 33m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1359441</t>
+          <t>TKT1358369</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Shivam Rajbanshi</t>
+          <t>Tanushi Agrawal</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -7624,22 +8117,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:47:08 PM</t>
+          <t>07 Oct 2026 02:14:46 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 02:08:34 PM</t>
+          <t>04 Oct 2026 05:04:41 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:47:08 PM</t>
+          <t>07 Oct 2026 02:14:46 PM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -7649,74 +8142,409 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2d 38m</t>
+          <t>2d 21h 10m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
+          <t>TKT1358082</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Sarita Kathet</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:31:51 PM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:31:51 PM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:00:30 PM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>2d 23h 28m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>2d 23h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361680</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Pranish Shrestha</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:28:56 PM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:12:30 AM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:28:56 PM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1359441</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Shivam Rajbanshi</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:47:08 PM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 02:08:34 PM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:47:08 PM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>2d 38m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
           <t>TKT1359387</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Sunil Maharjan</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>Case : Router setup  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router setup  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>07 Oct 2026 03:41:20 PM</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>05 Oct 2026 01:36:59 PM</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K40" s="3" t="inlineStr">
         <is>
           <t>07 Oct 2026 03:41:20 PM</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="L40" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="M40" s="3" t="inlineStr">
         <is>
           <t>2d 2h 4m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1360830</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Chandan shrestha</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>General Query &amp; Feedback</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Case : lan port not working  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : lan port not working  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 06:25:23 PM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 03:37:04 PM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:47:51 PM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>21h 22m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>1d 10m</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360404</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Manju Ghising</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Case : nettv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : nettv issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:47:23 PM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 11:08:05 AM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:47:23 PM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 39m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW37"/>
+  <dimension ref="A1:AW38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6500,10 +6500,8 @@
           <t>Ram Sharan Khatri</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9841367090</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9841367090</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -6538,10 +6536,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>27.6851</t>
-        </is>
+      <c r="Y35" s="3" t="n">
+        <v>27.6851</v>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
@@ -6593,25 +6589,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>2,6</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>85.33957</t>
-        </is>
+      <c r="AP35" s="3" t="n">
+        <v>85.33956999999999</v>
       </c>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -6707,10 +6699,8 @@
           <t>Chandan shrestha</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9849210578</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9849210578</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -6745,10 +6735,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.73385</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.73385</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -6786,10 +6774,8 @@
           <t>General Query &amp; Feedback</t>
         </is>
       </c>
-      <c r="AH36" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH36" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
@@ -6808,25 +6794,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>CDB436</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.29008</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.29008</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : lan port not working  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -6912,20 +6894,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M37" s="3" t="inlineStr"/>
       <c r="N37" s="3" t="inlineStr">
         <is>
           <t>Manju Ghising</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9819354646</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9819354646</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -6960,10 +6936,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>27.67617</t>
-        </is>
+      <c r="Y37" s="3" t="n">
+        <v>27.67617</v>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
@@ -7015,50 +6989,253 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>L28-2</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.37756</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.37756</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 39m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
           <t>Case : nettv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS37" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>1d 4h 39m</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV37" s="3" t="inlineStr">
-        <is>
-          <t>Case : nettv issue   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 4:14 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360620</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Hira Lal Shrestha</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Hira Lal Shrestha</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9841556365</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:23:25 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9841556365</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:23:25 PM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:14:36 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>27.70704</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>27.70691, 85.30571, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr"/>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>12:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>CDB384</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>85.30578</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 51m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 51m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7110,7 +7287,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -7120,7 +7297,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -7131,7 +7308,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.2%</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7320,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10h 54m</t>
+          <t>11h 53m</t>
         </is>
       </c>
     </row>
@@ -7155,7 +7332,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 15h 40m</t>
+          <t>1d 14h 52m</t>
         </is>
       </c>
     </row>
@@ -7196,14 +7373,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -7327,14 +7504,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8624,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Case : lan port not working  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -8514,14 +8691,14 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
           <t>Case : nettv issue   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>Case : nettv issue   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
           <t>07 Oct 2026 03:47:23 PM</t>
@@ -8545,6 +8722,73 @@
       <c r="M42" s="3" t="inlineStr">
         <is>
           <t>1d 4h 39m</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TKT1360620</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Hira Lal Shrestha</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:23:25 PM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:23:25 PM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:14:36 PM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>1d 2h 51m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>1d 2h 51m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW38"/>
+  <dimension ref="A1:AW40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -7099,10 +7099,8 @@
           <t>Hira Lal Shrestha</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9841556365</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9841556365</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -7137,10 +7135,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>27.70704</t>
-        </is>
+      <c r="Y38" s="3" t="n">
+        <v>27.70704</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
@@ -7192,48 +7188,462 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>CDB384</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>85.30578</t>
-        </is>
+      <c r="AP38" s="3" t="n">
+        <v>85.30578</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 51m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 51m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS38" s="3" t="inlineStr">
-        <is>
-          <t>1d 2h 51m</t>
-        </is>
-      </c>
-      <c r="AT38" s="3" t="inlineStr">
-        <is>
-          <t>1d 2h 51m</t>
-        </is>
-      </c>
-      <c r="AU38" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV38" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 4:19 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wIfI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>wIfI 6</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359540</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Rukshana Maharjan</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Rukshana Maharjan</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9866276517</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:19:38 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>9866276517</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:25:17 PM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:19:38 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t>27.63512</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>Near Harisiddhi Punya Udaya Bihar ,Unnamed Road, J8PR+27F, ??????? 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr"/>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>20:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>3,15</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>85.3405</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wIfI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>2d 54m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wIfI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 4:20 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router upgarde  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 router upgarde</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359412</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Kirtan Shrestha</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Kirtan Shrestha</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9863213432</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:20:16 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>9863213432</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:49:00 PM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:20:16 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t>27.68816</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>New Baneshwor , Buddhanagar , Lumbini Galli , Near Tandukar Store , opp R.K. Boys Hostel , Bagmati,</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr">
+        <is>
+          <t>kirtanstha02@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>22:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Sagar Khadka</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>CDB293</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>85.32974</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router upgarde  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 31m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router upgarde  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -7250,7 +7660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7287,7 +7697,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -7297,7 +7707,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -7308,7 +7718,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7730,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>11h 53m</t>
+          <t>10h 34m</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7742,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 14h 52m</t>
+          <t>1d 16h 4m</t>
         </is>
       </c>
     </row>
@@ -7373,14 +7783,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>56.5%</t>
         </is>
       </c>
     </row>
@@ -7504,14 +7914,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -8758,14 +9168,14 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>06 Oct 2026 01:23:25 PM</t>
@@ -8789,6 +9199,140 @@
       <c r="M43" s="5" t="inlineStr">
         <is>
           <t>1d 2h 51m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359540</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Rukshana Maharjan</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wIfI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wIfI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:19:38 PM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:25:17 PM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:19:38 PM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>2d 54m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TKT1359412</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Kirtan Shrestha</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router upgarde  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router upgarde  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:20:16 PM</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:49:00 PM</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:20:16 PM</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>2d 2h 31m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW40"/>
+  <dimension ref="A1:AW43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7298,10 +7298,8 @@
           <t>Rukshana Maharjan</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9866276517</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9866276517</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -7336,10 +7334,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t>27.63512</t>
-        </is>
+      <c r="Y39" s="3" t="n">
+        <v>27.63512</v>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
@@ -7391,25 +7387,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
           <t>3,15</t>
         </is>
       </c>
-      <c r="AP39" s="3" t="inlineStr">
-        <is>
-          <t>85.3405</t>
-        </is>
+      <c r="AP39" s="3" t="n">
+        <v>85.34050000000001</v>
       </c>
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>Case : wIfI 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
@@ -7505,10 +7497,8 @@
           <t>Kirtan Shrestha</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9863213432</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9863213432</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -7543,10 +7533,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t>27.68816</t>
-        </is>
+      <c r="Y40" s="3" t="n">
+        <v>27.68816</v>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
@@ -7602,50 +7590,675 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
           <t>CDB293</t>
         </is>
       </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>85.32974</t>
-        </is>
+      <c r="AP40" s="3" t="n">
+        <v>85.32974</v>
       </c>
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 31m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 router upgarde  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS40" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT40" s="3" t="inlineStr">
-        <is>
-          <t>2d 2h 31m</t>
-        </is>
-      </c>
-      <c r="AU40" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV40" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 router upgarde  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW40" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 4:44 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359185</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Parbati Ghale</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Parbati Ghale</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9841022579</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:38:20 AM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9841022579</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:38:20 AM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:44:41 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.696636</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Near Salik Chowk ParkKalanki, Kathmandu 44600, , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>prashanghale60@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr"/>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>CDB324</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.277157</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>2d 5h 6m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>2d 5h 6m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 4:39 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : adapter issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>adapter issue</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361288</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Chitiz ale magar</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Chitiz ale magar</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9843481430</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 09:29:22 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9843481430</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 09:25:43 PM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:39:06 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.743249</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Nepaltar near Nepal gas, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr"/>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>06:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Anusha Adhikari</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>L37-3</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.304097</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : adapter issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>19h 9m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>19h 13m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : adapter issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 4:38 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : adapter issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>adapter issue</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361288</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Chitiz ale magar</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Chitiz ale magar</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9843481430</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 09:29:22 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9843481430</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 09:25:43 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:39:06 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>27.743249</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Nepaltar near Nepal gas, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr"/>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>06:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Anusha Adhikari</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>L37-3</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>85.304097</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : adapter issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>19h 9m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>19h 13m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : adapter issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -7660,7 +8273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7697,7 +8310,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -7707,7 +8320,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -7718,7 +8331,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>47.6%</t>
         </is>
       </c>
     </row>
@@ -7730,7 +8343,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10h 34m</t>
+          <t>11h 26m</t>
         </is>
       </c>
     </row>
@@ -7742,7 +8355,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 16h 4m</t>
+          <t>1d 13h 59m</t>
         </is>
       </c>
     </row>
@@ -7783,14 +8396,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>13</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -7801,10 +8414,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -7914,14 +8527,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>12</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>52.2%</t>
         </is>
       </c>
     </row>
@@ -7960,10 +8573,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -9235,7 +9848,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Case : wIfI 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -9302,14 +9915,14 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 router upgarde  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 router upgarde  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
           <t>07 Oct 2026 04:20:16 PM</t>
@@ -9333,6 +9946,140 @@
       <c r="M45" s="5" t="inlineStr">
         <is>
           <t>2d 2h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361288</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Chitiz ale magar</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Case : adapter issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : adapter issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 09:29:22 PM</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 09:25:43 PM</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:39:06 PM</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>19h 9m</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>19h 13m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TKT1361288</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Chitiz ale magar</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Case : adapter issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Case : adapter issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 09:29:22 PM</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 09:25:43 PM</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:39:06 PM</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>19h 9m</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>19h 13m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW43"/>
+  <dimension ref="A1:AW45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7700,10 +7700,8 @@
           <t>Parbati Ghale</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9841022579</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9841022579</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -7738,10 +7736,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>27.696636</t>
-        </is>
+      <c r="Y41" s="3" t="n">
+        <v>27.696636</v>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
@@ -7793,25 +7789,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>CDB324</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.277157</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.277157</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -7907,10 +7899,8 @@
           <t>Chitiz ale magar</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9843481430</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9843481430</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -7945,10 +7935,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t>27.743249</t>
-        </is>
+      <c r="Y42" s="3" t="n">
+        <v>27.743249</v>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
@@ -7982,10 +7970,8 @@
           <t>Router Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="AH42" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH42" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
@@ -8004,25 +7990,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>L37-3</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.304097</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.304097</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : adapter issue   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
@@ -8118,10 +8100,8 @@
           <t>Chitiz ale magar</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9843481430</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9843481430</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -8156,10 +8136,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>27.743249</t>
-        </is>
+      <c r="Y43" s="3" t="n">
+        <v>27.743249</v>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
@@ -8193,10 +8171,8 @@
           <t>Router Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="AH43" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH43" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI43" s="3" t="inlineStr">
         <is>
@@ -8215,48 +8191,358 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>L37-3</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>85.304097</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>85.304097</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>19h 9m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>19h 13m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
           <t>Case : adapter issue   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS43" s="3" t="inlineStr">
-        <is>
-          <t>19h 9m</t>
-        </is>
-      </c>
-      <c r="AT43" s="3" t="inlineStr">
-        <is>
-          <t>19h 13m</t>
-        </is>
-      </c>
-      <c r="AU43" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV43" s="3" t="inlineStr">
-        <is>
-          <t>Case : adapter issue   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 4:49 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
+      <c r="AA44" s="3" t="inlineStr"/>
+      <c r="AB44" s="3" t="inlineStr"/>
+      <c r="AC44" s="3" t="inlineStr"/>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr"/>
+      <c r="AF44" s="3" t="inlineStr"/>
+      <c r="AG44" s="3" t="inlineStr"/>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr"/>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr"/>
+      <c r="AM44" s="3" t="inlineStr"/>
+      <c r="AN44" s="3" t="inlineStr"/>
+      <c r="AO44" s="3" t="inlineStr"/>
+      <c r="AP44" s="3" t="inlineStr"/>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 4:54 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>NO LIGHT ISSUE</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362084</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Anu Devi Kalwar</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Anu Devi Kalwar</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9824275195</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:54:55 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>BKT9824275195</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:00:06 PM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:54:55 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>27.678078213298548, 85.36204196309227, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>9824275195@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>01:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>L3-3</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>1h 54m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -8273,7 +8559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8310,7 +8596,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -8320,7 +8606,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -8331,7 +8617,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.7%</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8629,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>11h 26m</t>
+          <t>10h 53m</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8641,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 13h 59m</t>
+          <t>1d 12h 16m</t>
         </is>
       </c>
     </row>
@@ -8414,10 +8700,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -8573,10 +8859,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -9982,7 +10268,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Case : adapter issue   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -10049,14 +10335,14 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
           <t>Case : adapter issue   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>Case : adapter issue   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
           <t>06 Oct 2026 09:29:22 PM</t>
@@ -10080,6 +10366,73 @@
       <c r="M47" s="5" t="inlineStr">
         <is>
           <t>19h 13m</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362084</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Anu Devi Kalwar</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:54:55 PM</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:00:06 PM</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:54:55 PM</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>1h 54m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW45"/>
+  <dimension ref="A1:AW46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8404,10 +8404,8 @@
           <t>Anu Devi Kalwar</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9824275195</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9824275195</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -8442,10 +8440,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
@@ -8501,48 +8497,251 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>L3-3</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>1h 54m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
           <t>Case : NO LIGHT ISSUE   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS45" s="3" t="inlineStr">
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 5:13 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359167</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Raju Khadk</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Raju Khadk</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9803184008</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 05:13:52 PM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>9803184008</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:27:59 AM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 05:13:52 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>27.67761</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>Koteshwor, Kathmandu, Bagmati, Central, Nepal, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr"/>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>01:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>85.34567</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT45" s="3" t="inlineStr">
-        <is>
-          <t>1h 54m</t>
-        </is>
-      </c>
-      <c r="AU45" s="3" t="inlineStr">
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>2d 5h 45m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV45" s="3" t="inlineStr">
-        <is>
-          <t>Case : NO LIGHT ISSUE   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW45" s="3" t="inlineStr">
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -8559,7 +8758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8596,7 +8795,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -8606,7 +8805,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -8617,7 +8816,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>48.9%</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8828,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10h 53m</t>
+          <t>10h 23m</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8840,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 12h 16m</t>
+          <t>1d 13h 4m</t>
         </is>
       </c>
     </row>
@@ -8682,14 +8881,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
     </row>
@@ -8813,14 +9012,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -10402,14 +10601,14 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
           <t>Case : NO LIGHT ISSUE   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>Case : NO LIGHT ISSUE   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
           <t>07 Oct 2026 04:54:55 PM</t>
@@ -10433,6 +10632,73 @@
       <c r="M48" s="3" t="inlineStr">
         <is>
           <t>1h 54m</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>TKT1359167</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Raju Khadk</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 05:13:52 PM</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:27:59 AM</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 05:13:52 PM</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>2d 5h 45m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW46"/>
+  <dimension ref="A1:AW47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -513,7 +513,7 @@
     <col width="19" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="24" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="21" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="11" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
@@ -532,7 +532,7 @@
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="36" customWidth="1" min="47" max="47"/>
+    <col width="40" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -8607,10 +8607,8 @@
           <t>Raju Khadk</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9803184008</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9803184008</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -8645,10 +8643,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>27.67761</t>
-        </is>
+      <c r="Y46" s="3" t="n">
+        <v>27.67761</v>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
@@ -8700,50 +8696,249 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>1,3</t>
         </is>
       </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>85.34567</t>
-        </is>
+      <c r="AP46" s="3" t="n">
+        <v>85.34567</v>
       </c>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>2d 5h 45m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
           <t>Case : Router upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS46" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT46" s="3" t="inlineStr">
-        <is>
-          <t>2d 5h 45m</t>
-        </is>
-      </c>
-      <c r="AU46" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV46" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW46" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 5:18 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358074</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Gobinda Bahadur Adhikari</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Gobinda Bahadur Adhikari</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9851109641</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 05:18:34 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9860172330</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:28:25 PM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 05:21:28 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr"/>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Green Wood Villas - Housing complex M7PH+QQ4 Kirtipur 44618, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>krishnakhanal1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>03:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>CDB047</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr"/>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>2m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 53m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Assigned / Transferred to MS / Other Handler</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -8758,7 +8953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8766,7 +8961,7 @@
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
@@ -8795,7 +8990,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -8805,7 +9000,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -8816,7 +9011,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8828,7 +9023,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10h 23m</t>
+          <t>9h 56m</t>
         </is>
       </c>
     </row>
@@ -8840,7 +9035,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 13h 4m</t>
+          <t>1d 14h 42m</t>
         </is>
       </c>
     </row>
@@ -8881,14 +9076,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>57.7%</t>
         </is>
       </c>
     </row>
@@ -9012,14 +9207,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
     </row>
@@ -10668,14 +10863,14 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
           <t>Case : Router upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
           <t>07 Oct 2026 05:13:52 PM</t>
@@ -10699,6 +10894,73 @@
       <c r="M49" s="5" t="inlineStr">
         <is>
           <t>2d 5h 45m</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358074</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Gobinda Bahadur Adhikari</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Assigned / Transferred to MS / Other Handler</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 05:18:34 PM</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:28:25 PM</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 05:21:28 PM</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>2m</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 53m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW47"/>
+  <dimension ref="A1:AW48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="19" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="24" customWidth="1" min="27" max="27"/>
     <col width="21" customWidth="1" min="28" max="28"/>
@@ -8806,10 +8806,8 @@
           <t>Gobinda Bahadur Adhikari</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9851109641</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9851109641</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -8899,10 +8897,8 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
@@ -8913,32 +8909,243 @@
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>2m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 53m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Assigned / Transferred to MS / Other Handler</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS47" s="3" t="inlineStr">
-        <is>
-          <t>2m</t>
-        </is>
-      </c>
-      <c r="AT47" s="3" t="inlineStr">
-        <is>
-          <t>3d 2h 53m</t>
-        </is>
-      </c>
-      <c r="AU47" s="3" t="inlineStr">
-        <is>
-          <t>Assigned / Transferred to MS / Other Handler</t>
-        </is>
-      </c>
-      <c r="AV47" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW47" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 5:41 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>router change</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358408</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh maharhatn</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9851234730</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 05:41:03 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>LTP9851234730</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:30:07 PM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 05:41:03 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>27.678663629123296</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>lalitpur balkumari , , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>raje6@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>03:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>CDB624</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>85.31776428222658</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>3d 10m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -8953,7 +9160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8990,7 +9197,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -9000,7 +9207,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -9011,7 +9218,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.1%</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9230,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9h 56m</t>
+          <t>9h 31m</t>
         </is>
       </c>
     </row>
@@ -9035,7 +9242,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 14h 42m</t>
+          <t>1d 16h 6m</t>
         </is>
       </c>
     </row>
@@ -9076,14 +9283,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>59.3%</t>
         </is>
       </c>
     </row>
@@ -9207,14 +9414,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>57.7%</t>
         </is>
       </c>
     </row>
@@ -10930,14 +11137,14 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
           <t>07 Oct 2026 05:18:34 PM</t>
@@ -10961,6 +11168,73 @@
       <c r="M50" s="3" t="inlineStr">
         <is>
           <t>3d 2h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TKT1358408</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 05:41:03 PM</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:30:07 PM</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 05:41:03 PM</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>3d 10m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW48"/>
+  <dimension ref="A1:AW50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="21" customWidth="1" min="25" max="25"/>
+    <col width="19" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="24" customWidth="1" min="27" max="27"/>
     <col width="21" customWidth="1" min="28" max="28"/>
@@ -9005,10 +9005,8 @@
           <t>Rajesh maharhatn</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9851234730</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9851234730</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -9043,10 +9041,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>27.678663629123296</t>
-        </is>
+      <c r="Y48" s="3" t="n">
+        <v>27.6786636291233</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
@@ -9102,50 +9098,468 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
           <t>CDB624</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>85.31776428222658</t>
-        </is>
+      <c r="AP48" s="3" t="n">
+        <v>85.31776428222658</v>
       </c>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>3d 10m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
           <t>Case : router change   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS48" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT48" s="3" t="inlineStr">
-        <is>
-          <t>3d 10m</t>
-        </is>
-      </c>
-      <c r="AU48" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV48" s="3" t="inlineStr">
-        <is>
-          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW48" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 5:58 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358919</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Gautam</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Gautam</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9841356242</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:48:31 AM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9841356242</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:48:31 AM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 05:58:06 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>27.6869</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki CDB 444, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>gautam.shanta@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>03:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>85.27633</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>2d 9h 9m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>2d 9h 9m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 5:57 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358919</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Gautam</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Gautam</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9841356242</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:48:31 AM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>9841356242</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:48:31 AM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 05:58:06 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>27.6869</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki CDB 444, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>gautam.shanta@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr">
+        <is>
+          <t>03:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>85.27633</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>2d 9h 9m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>2d 9h 9m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -9160,7 +9574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9197,7 +9611,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -9207,7 +9621,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -9218,7 +9632,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>53.1%</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9644,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9h 31m</t>
+          <t>13h 11m</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9656,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 16h 6m</t>
+          <t>1d 17h 25m</t>
         </is>
       </c>
     </row>
@@ -9283,14 +9697,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>
@@ -9414,14 +9828,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>60.7%</t>
         </is>
       </c>
     </row>
@@ -11204,14 +11618,14 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
           <t>Case : router change   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
           <t>07 Oct 2026 05:41:03 PM</t>
@@ -11235,6 +11649,140 @@
       <c r="M51" s="5" t="inlineStr">
         <is>
           <t>3d 10m</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358919</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Gautam</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:48:31 AM</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:48:31 AM</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 05:58:06 PM</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>2d 9h 9m</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>2d 9h 9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>TKT1358919</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Shanta Gautam</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:48:31 AM</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:48:31 AM</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 05:58:06 PM</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>2d 9h 9m</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>2d 9h 9m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="40" customWidth="1" min="47" max="47"/>
@@ -9208,10 +9208,8 @@
           <t>Shanta Gautam</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9841356242</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9841356242</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -9246,10 +9244,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y49" s="3" t="inlineStr">
-        <is>
-          <t>27.6869</t>
-        </is>
+      <c r="Y49" s="3" t="n">
+        <v>27.6869</v>
       </c>
       <c r="Z49" s="3" t="inlineStr">
         <is>
@@ -9305,25 +9301,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>3,3</t>
         </is>
       </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>85.27633</t>
-        </is>
+      <c r="AP49" s="3" t="n">
+        <v>85.27633</v>
       </c>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
@@ -9419,10 +9411,8 @@
           <t>Shanta Gautam</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9841356242</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9841356242</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -9457,10 +9447,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y50" s="3" t="inlineStr">
-        <is>
-          <t>27.6869</t>
-        </is>
+      <c r="Y50" s="3" t="n">
+        <v>27.6869</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
@@ -9516,25 +9504,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
           <t>3,3</t>
         </is>
       </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>85.27633</t>
-        </is>
+      <c r="AP50" s="3" t="n">
+        <v>85.27633</v>
       </c>
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
@@ -9583,7 +9567,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -11685,7 +11669,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -11752,7 +11736,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW50"/>
+  <dimension ref="A1:AW51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="40" customWidth="1" min="47" max="47"/>
@@ -9547,6 +9547,217 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 6:24 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359965</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Sita Bhattarai</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Sita Bhattarai</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9808621260</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 06:24:04 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>9808621260</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:09:50 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 06:24:04 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>27.64685</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>Nakhipot, Lalitpur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>siteydesigns@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>18:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr">
+        <is>
+          <t>85.31508</t>
+        </is>
+      </c>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 14m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9558,7 +9769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9567,7 +9778,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9595,7 +9806,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -9605,7 +9816,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -9616,7 +9827,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>54.0%</t>
         </is>
       </c>
     </row>
@@ -9628,7 +9839,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>13h 11m</t>
+          <t>12h 42m</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9851,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 17h 25m</t>
+          <t>1d 17h 33m</t>
         </is>
       </c>
     </row>
@@ -9681,14 +9892,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>63.3%</t>
         </is>
       </c>
     </row>
@@ -9812,14 +10023,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>
@@ -11770,6 +11981,73 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359965</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Sita Bhattarai</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 06:24:04 PM</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:09:50 PM</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 06:24:04 PM</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 14m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_07_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_07_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="40" customWidth="1" min="47" max="47"/>
@@ -9614,10 +9614,8 @@
           <t>Sita Bhattarai</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9808621260</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9808621260</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -9652,10 +9650,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y51" s="3" t="inlineStr">
-        <is>
-          <t>27.64685</t>
-        </is>
+      <c r="Y51" s="3" t="n">
+        <v>27.64685</v>
       </c>
       <c r="Z51" s="3" t="inlineStr">
         <is>
@@ -9711,25 +9707,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
           <t>3,3</t>
         </is>
       </c>
-      <c r="AP51" s="3" t="inlineStr">
-        <is>
-          <t>85.31508</t>
-        </is>
+      <c r="AP51" s="3" t="n">
+        <v>85.31507999999999</v>
       </c>
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
@@ -9778,7 +9770,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -12014,7 +12006,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
